--- a/Documentation/Best For Weighting Tables/Best for Tech Savvy Seniors.xlsx
+++ b/Documentation/Best For Weighting Tables/Best for Tech Savvy Seniors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7762420F-1E9E-4B3F-80BE-FAD32ED05408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA9751C-CED8-4B35-BB99-F0F57908BD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="2160" windowWidth="21600" windowHeight="11295" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Best for Tech-Savvy Seniors" sheetId="1" r:id="rId1"/>
@@ -484,7 +484,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +524,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="4">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
